--- a/Excel/Payroll.xlsx
+++ b/Excel/Payroll.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Tests\j-l-data-science-data-analytics\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{726AE16B-FC21-4582-800B-62FF8BF89EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01957A3D-E6A6-4D3F-857F-6DDB229191A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F7F01B57-B888-4E05-A171-2C1A91DBF350}"/>
   </bookViews>
@@ -314,11 +314,11 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -657,10 +657,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="19"/>
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21"/>
       <c r="C1" t="s">
         <v>27</v>
       </c>
@@ -807,19 +807,19 @@
       </c>
       <c r="E4" s="5">
         <f ca="1">RANDBETWEEN(10, 90)</f>
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="F4" s="5">
         <f t="shared" ref="F4:H4" ca="1" si="5">RANDBETWEEN(10, 90)</f>
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="G4" s="5">
         <f t="shared" ca="1" si="5"/>
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="H4" s="5">
         <f t="shared" ca="1" si="5"/>
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="I4" s="7">
         <f t="shared" ref="I4:I20" si="6">IF(D4&gt;50,D4-50,0)</f>
@@ -827,15 +827,15 @@
       </c>
       <c r="J4" s="7">
         <f t="shared" ref="J4:J20" ca="1" si="7">IF(E4&gt;50,E4-50,0)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K4" s="7">
         <f t="shared" ref="K4:K20" ca="1" si="8">IF(F4&gt;50,F4-50,0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L4" s="7">
         <f t="shared" ref="L4:L20" ca="1" si="9">IF(G4&gt;50,G4-50,0)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M4" s="7">
         <f t="shared" ref="M4:M20" ca="1" si="10">IF(H4&gt;50,H4-50,0)</f>
@@ -847,19 +847,19 @@
       </c>
       <c r="O4" s="9">
         <f ca="1">$C4*E4</f>
-        <v>6000</v>
+        <v>4700</v>
       </c>
       <c r="P4" s="9">
         <f t="shared" ref="P4:R19" ca="1" si="11">$C4*F4</f>
-        <v>4000</v>
+        <v>5500</v>
       </c>
       <c r="Q4" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>3100</v>
+        <v>7500</v>
       </c>
       <c r="R4" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>1600</v>
+        <v>3700</v>
       </c>
       <c r="S4" s="11">
         <f>0.5*$C4*I4</f>
@@ -867,15 +867,15 @@
       </c>
       <c r="T4" s="11">
         <f ca="1">0.5*$C4*J4</f>
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="U4" s="11">
         <f t="shared" ref="U4:W19" ca="1" si="12">0.5*$C4*K4</f>
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="V4" s="11">
         <f t="shared" ca="1" si="12"/>
-        <v>0</v>
+        <v>1250</v>
       </c>
       <c r="W4" s="14">
         <f t="shared" ca="1" si="12"/>
@@ -887,24 +887,24 @@
       </c>
       <c r="Y4" s="18">
         <f t="shared" ref="Y4:AB19" ca="1" si="14">O4+T4</f>
-        <v>6500</v>
+        <v>4700</v>
       </c>
       <c r="Z4" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>4000</v>
+        <v>5750</v>
       </c>
       <c r="AA4" s="18">
         <f ca="1">Q4+V4</f>
-        <v>3100</v>
+        <v>8750</v>
       </c>
       <c r="AB4" s="18">
         <f ca="1">R4+W4</f>
-        <v>1600</v>
+        <v>3700</v>
       </c>
       <c r="AC4" s="16"/>
       <c r="AD4" s="2">
         <f ca="1">SUM(X4:AB4)</f>
-        <v>19200</v>
+        <v>26900</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.3">
@@ -922,19 +922,19 @@
       </c>
       <c r="E5" s="5">
         <f t="shared" ref="E5:H20" ca="1" si="15">RANDBETWEEN(10, 90)</f>
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F5" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="G5" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="H5" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="I5" s="7">
         <f t="shared" si="6"/>
@@ -942,19 +942,19 @@
       </c>
       <c r="J5" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K5" s="7">
         <f t="shared" ca="1" si="8"/>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L5" s="7">
         <f t="shared" ca="1" si="9"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M5" s="7">
         <f t="shared" ca="1" si="10"/>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="N5" s="9">
         <f t="shared" ref="N5:N20" si="16">$C5*D5</f>
@@ -962,19 +962,19 @@
       </c>
       <c r="O5" s="9">
         <f t="shared" ref="O5:O20" ca="1" si="17">$C5*E5</f>
-        <v>12000</v>
+        <v>12600</v>
       </c>
       <c r="P5" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>11100</v>
+        <v>7500</v>
       </c>
       <c r="Q5" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>7200</v>
+        <v>12600</v>
       </c>
       <c r="R5" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>10050</v>
+        <v>9150</v>
       </c>
       <c r="S5" s="11">
         <f t="shared" ref="S5:T20" si="18">0.5*$C5*I5</f>
@@ -982,19 +982,19 @@
       </c>
       <c r="T5" s="11">
         <f t="shared" ca="1" si="18"/>
-        <v>2250</v>
+        <v>2550</v>
       </c>
       <c r="U5" s="11">
         <f t="shared" ca="1" si="12"/>
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="V5" s="11">
         <f t="shared" ca="1" si="12"/>
-        <v>0</v>
+        <v>2550</v>
       </c>
       <c r="W5" s="15">
         <f t="shared" ca="1" si="12"/>
-        <v>1275</v>
+        <v>825</v>
       </c>
       <c r="X5" s="18">
         <f t="shared" si="13"/>
@@ -1002,24 +1002,24 @@
       </c>
       <c r="Y5" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>14250</v>
+        <v>15150</v>
       </c>
       <c r="Z5" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>12900</v>
+        <v>7500</v>
       </c>
       <c r="AA5" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>7200</v>
+        <v>15150</v>
       </c>
       <c r="AB5" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>11325</v>
+        <v>9975</v>
       </c>
       <c r="AC5" s="16"/>
       <c r="AD5" s="2">
         <f t="shared" ref="AD5:AD20" ca="1" si="19">SUM(X5:AB5)</f>
-        <v>51750</v>
+        <v>53850</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.3">
@@ -1037,19 +1037,19 @@
       </c>
       <c r="E6" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="F6" s="5">
         <f t="shared" ca="1" si="15"/>
+        <v>90</v>
+      </c>
+      <c r="G6" s="5">
+        <f t="shared" ca="1" si="15"/>
         <v>82</v>
       </c>
-      <c r="G6" s="5">
-        <f t="shared" ca="1" si="15"/>
-        <v>81</v>
-      </c>
       <c r="H6" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I6" s="7">
         <f t="shared" si="6"/>
@@ -1057,15 +1057,15 @@
       </c>
       <c r="J6" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K6" s="7">
         <f t="shared" ca="1" si="8"/>
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L6" s="7">
         <f t="shared" ca="1" si="9"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M6" s="7">
         <f t="shared" ca="1" si="10"/>
@@ -1077,19 +1077,19 @@
       </c>
       <c r="O6" s="9">
         <f t="shared" ca="1" si="17"/>
-        <v>12000</v>
+        <v>9200</v>
       </c>
       <c r="P6" s="9">
         <f t="shared" ca="1" si="11"/>
+        <v>18000</v>
+      </c>
+      <c r="Q6" s="9">
+        <f t="shared" ca="1" si="11"/>
         <v>16400</v>
       </c>
-      <c r="Q6" s="9">
-        <f t="shared" ca="1" si="11"/>
-        <v>16200</v>
-      </c>
       <c r="R6" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>6000</v>
+        <v>2600</v>
       </c>
       <c r="S6" s="11">
         <f t="shared" si="18"/>
@@ -1097,15 +1097,15 @@
       </c>
       <c r="T6" s="11">
         <f t="shared" ca="1" si="18"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="U6" s="11">
         <f t="shared" ca="1" si="12"/>
+        <v>4000</v>
+      </c>
+      <c r="V6" s="11">
+        <f t="shared" ca="1" si="12"/>
         <v>3200</v>
-      </c>
-      <c r="V6" s="11">
-        <f t="shared" ca="1" si="12"/>
-        <v>3100</v>
       </c>
       <c r="W6" s="15">
         <f t="shared" ca="1" si="12"/>
@@ -1117,24 +1117,24 @@
       </c>
       <c r="Y6" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>13000</v>
+        <v>9200</v>
       </c>
       <c r="Z6" s="18">
         <f t="shared" ca="1" si="14"/>
+        <v>22000</v>
+      </c>
+      <c r="AA6" s="18">
+        <f t="shared" ca="1" si="14"/>
         <v>19600</v>
       </c>
-      <c r="AA6" s="18">
-        <f t="shared" ca="1" si="14"/>
-        <v>19300</v>
-      </c>
       <c r="AB6" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>6000</v>
+        <v>2600</v>
       </c>
       <c r="AC6" s="16"/>
       <c r="AD6" s="2">
         <f t="shared" ca="1" si="19"/>
-        <v>66900</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.3">
@@ -1152,15 +1152,15 @@
       </c>
       <c r="E7" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="F7" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="G7" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="H7" s="5">
         <f t="shared" ca="1" si="15"/>
@@ -1172,15 +1172,15 @@
       </c>
       <c r="J7" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K7" s="7">
         <f t="shared" ca="1" si="8"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L7" s="7">
         <f t="shared" ca="1" si="9"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M7" s="7">
         <f t="shared" ca="1" si="10"/>
@@ -1192,15 +1192,15 @@
       </c>
       <c r="O7" s="9">
         <f t="shared" ca="1" si="17"/>
-        <v>21000</v>
+        <v>11500</v>
       </c>
       <c r="P7" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>13750</v>
+        <v>11750</v>
       </c>
       <c r="Q7" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>11750</v>
+        <v>15500</v>
       </c>
       <c r="R7" s="9">
         <f t="shared" ca="1" si="11"/>
@@ -1212,15 +1212,15 @@
       </c>
       <c r="T7" s="11">
         <f t="shared" ca="1" si="18"/>
-        <v>4250</v>
+        <v>0</v>
       </c>
       <c r="U7" s="11">
         <f t="shared" ca="1" si="12"/>
-        <v>625</v>
+        <v>0</v>
       </c>
       <c r="V7" s="11">
         <f t="shared" ca="1" si="12"/>
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="W7" s="15">
         <f t="shared" ca="1" si="12"/>
@@ -1232,15 +1232,15 @@
       </c>
       <c r="Y7" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>25250</v>
+        <v>11500</v>
       </c>
       <c r="Z7" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>14375</v>
+        <v>11750</v>
       </c>
       <c r="AA7" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>11750</v>
+        <v>17000</v>
       </c>
       <c r="AB7" s="18">
         <f t="shared" ca="1" si="14"/>
@@ -1249,7 +1249,7 @@
       <c r="AC7" s="16"/>
       <c r="AD7" s="2">
         <f t="shared" ca="1" si="19"/>
-        <v>79375</v>
+        <v>68250</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.3">
@@ -1267,19 +1267,19 @@
       </c>
       <c r="E8" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="F8" s="5">
         <f t="shared" ca="1" si="15"/>
+        <v>12</v>
+      </c>
+      <c r="G8" s="5">
+        <f t="shared" ca="1" si="15"/>
+        <v>48</v>
+      </c>
+      <c r="H8" s="5">
+        <f t="shared" ca="1" si="15"/>
         <v>78</v>
-      </c>
-      <c r="G8" s="5">
-        <f t="shared" ca="1" si="15"/>
-        <v>18</v>
-      </c>
-      <c r="H8" s="5">
-        <f t="shared" ca="1" si="15"/>
-        <v>65</v>
       </c>
       <c r="I8" s="7">
         <f t="shared" si="6"/>
@@ -1287,11 +1287,11 @@
       </c>
       <c r="J8" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K8" s="7">
         <f t="shared" ca="1" si="8"/>
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L8" s="7">
         <f t="shared" ca="1" si="9"/>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="M8" s="7">
         <f t="shared" ca="1" si="10"/>
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="N8" s="9">
         <f t="shared" si="16"/>
@@ -1307,19 +1307,19 @@
       </c>
       <c r="O8" s="9">
         <f t="shared" ca="1" si="17"/>
-        <v>16800</v>
+        <v>9300</v>
       </c>
       <c r="P8" s="9">
         <f t="shared" ca="1" si="11"/>
+        <v>3600</v>
+      </c>
+      <c r="Q8" s="9">
+        <f t="shared" ca="1" si="11"/>
+        <v>14400</v>
+      </c>
+      <c r="R8" s="9">
+        <f t="shared" ca="1" si="11"/>
         <v>23400</v>
-      </c>
-      <c r="Q8" s="9">
-        <f t="shared" ca="1" si="11"/>
-        <v>5400</v>
-      </c>
-      <c r="R8" s="9">
-        <f t="shared" ca="1" si="11"/>
-        <v>19500</v>
       </c>
       <c r="S8" s="11">
         <f t="shared" si="18"/>
@@ -1327,19 +1327,19 @@
       </c>
       <c r="T8" s="11">
         <f t="shared" ca="1" si="18"/>
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="U8" s="11">
         <f t="shared" ca="1" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="V8" s="11">
+        <f t="shared" ca="1" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="W8" s="15">
+        <f t="shared" ca="1" si="12"/>
         <v>4200</v>
-      </c>
-      <c r="V8" s="11">
-        <f t="shared" ca="1" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="W8" s="15">
-        <f t="shared" ca="1" si="12"/>
-        <v>2250</v>
       </c>
       <c r="X8" s="18">
         <f t="shared" si="13"/>
@@ -1347,24 +1347,24 @@
       </c>
       <c r="Y8" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>17700</v>
+        <v>9300</v>
       </c>
       <c r="Z8" s="18">
         <f t="shared" ca="1" si="14"/>
+        <v>3600</v>
+      </c>
+      <c r="AA8" s="18">
+        <f t="shared" ca="1" si="14"/>
+        <v>14400</v>
+      </c>
+      <c r="AB8" s="18">
+        <f t="shared" ca="1" si="14"/>
         <v>27600</v>
-      </c>
-      <c r="AA8" s="18">
-        <f t="shared" ca="1" si="14"/>
-        <v>5400</v>
-      </c>
-      <c r="AB8" s="18">
-        <f t="shared" ca="1" si="14"/>
-        <v>21750</v>
       </c>
       <c r="AC8" s="16"/>
       <c r="AD8" s="2">
         <f t="shared" ca="1" si="19"/>
-        <v>87450</v>
+        <v>69900</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.3">
@@ -1382,19 +1382,19 @@
       </c>
       <c r="E9" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="F9" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="H9" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="I9" s="7">
         <f t="shared" si="6"/>
@@ -1402,19 +1402,19 @@
       </c>
       <c r="J9" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K9" s="7">
         <f t="shared" ca="1" si="8"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L9" s="7">
         <f t="shared" ca="1" si="9"/>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M9" s="7">
         <f t="shared" ca="1" si="10"/>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="N9" s="9">
         <f t="shared" si="16"/>
@@ -1422,19 +1422,19 @@
       </c>
       <c r="O9" s="9">
         <f t="shared" ca="1" si="17"/>
-        <v>25900</v>
+        <v>10850</v>
       </c>
       <c r="P9" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>8050</v>
+        <v>24150</v>
       </c>
       <c r="Q9" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>28000</v>
+        <v>11550</v>
       </c>
       <c r="R9" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>12250</v>
+        <v>30800</v>
       </c>
       <c r="S9" s="11">
         <f t="shared" si="18"/>
@@ -1442,19 +1442,19 @@
       </c>
       <c r="T9" s="11">
         <f t="shared" ca="1" si="18"/>
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="U9" s="11">
         <f t="shared" ca="1" si="12"/>
-        <v>0</v>
+        <v>3325</v>
       </c>
       <c r="V9" s="11">
         <f t="shared" ca="1" si="12"/>
-        <v>5250</v>
+        <v>0</v>
       </c>
       <c r="W9" s="15">
         <f t="shared" ca="1" si="12"/>
-        <v>0</v>
+        <v>6650</v>
       </c>
       <c r="X9" s="18">
         <f t="shared" si="13"/>
@@ -1462,24 +1462,24 @@
       </c>
       <c r="Y9" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>30100</v>
+        <v>10850</v>
       </c>
       <c r="Z9" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>8050</v>
+        <v>27475</v>
       </c>
       <c r="AA9" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>33250</v>
+        <v>11550</v>
       </c>
       <c r="AB9" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>12250</v>
+        <v>37450</v>
       </c>
       <c r="AC9" s="16"/>
       <c r="AD9" s="2">
         <f t="shared" ca="1" si="19"/>
-        <v>101412.5</v>
+        <v>105087.5</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.3">
@@ -1497,19 +1497,19 @@
       </c>
       <c r="E10" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F10" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="G10" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="H10" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="I10" s="7">
         <f t="shared" si="6"/>
@@ -1525,11 +1525,11 @@
       </c>
       <c r="L10" s="7">
         <f t="shared" ca="1" si="9"/>
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="M10" s="7">
         <f t="shared" ca="1" si="10"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N10" s="9">
         <f t="shared" si="16"/>
@@ -1537,19 +1537,19 @@
       </c>
       <c r="O10" s="9">
         <f t="shared" ca="1" si="17"/>
-        <v>16800</v>
+        <v>15600</v>
       </c>
       <c r="P10" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>15600</v>
+        <v>10800</v>
       </c>
       <c r="Q10" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>22800</v>
+        <v>31200</v>
       </c>
       <c r="R10" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>6800</v>
+        <v>23200</v>
       </c>
       <c r="S10" s="11">
         <f t="shared" si="18"/>
@@ -1565,11 +1565,11 @@
       </c>
       <c r="V10" s="11">
         <f t="shared" ca="1" si="12"/>
-        <v>1400</v>
+        <v>5600</v>
       </c>
       <c r="W10" s="15">
         <f t="shared" ca="1" si="12"/>
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="X10" s="18">
         <f t="shared" si="13"/>
@@ -1577,24 +1577,24 @@
       </c>
       <c r="Y10" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>16800</v>
+        <v>15600</v>
       </c>
       <c r="Z10" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>15600</v>
+        <v>10800</v>
       </c>
       <c r="AA10" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>24200</v>
+        <v>36800</v>
       </c>
       <c r="AB10" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>6800</v>
+        <v>24800</v>
       </c>
       <c r="AC10" s="16"/>
       <c r="AD10" s="2">
         <f t="shared" ca="1" si="19"/>
-        <v>86400</v>
+        <v>111000</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.3">
@@ -1612,19 +1612,19 @@
       </c>
       <c r="E11" s="5">
         <f t="shared" ca="1" si="15"/>
+        <v>64</v>
+      </c>
+      <c r="F11" s="5">
+        <f t="shared" ca="1" si="15"/>
+        <v>73</v>
+      </c>
+      <c r="G11" s="5">
+        <f t="shared" ca="1" si="15"/>
         <v>11</v>
       </c>
-      <c r="F11" s="5">
-        <f t="shared" ca="1" si="15"/>
-        <v>35</v>
-      </c>
-      <c r="G11" s="5">
-        <f t="shared" ca="1" si="15"/>
-        <v>71</v>
-      </c>
       <c r="H11" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I11" s="7">
         <f t="shared" si="6"/>
@@ -1632,15 +1632,15 @@
       </c>
       <c r="J11" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K11" s="7">
         <f t="shared" ca="1" si="8"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L11" s="7">
         <f t="shared" ca="1" si="9"/>
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="M11" s="7">
         <f t="shared" ca="1" si="10"/>
@@ -1652,19 +1652,19 @@
       </c>
       <c r="O11" s="9">
         <f t="shared" ca="1" si="17"/>
+        <v>28800</v>
+      </c>
+      <c r="P11" s="9">
+        <f t="shared" ca="1" si="11"/>
+        <v>32850</v>
+      </c>
+      <c r="Q11" s="9">
+        <f t="shared" ca="1" si="11"/>
         <v>4950</v>
       </c>
-      <c r="P11" s="9">
-        <f t="shared" ca="1" si="11"/>
-        <v>15750</v>
-      </c>
-      <c r="Q11" s="9">
-        <f t="shared" ca="1" si="11"/>
-        <v>31950</v>
-      </c>
       <c r="R11" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>18900</v>
+        <v>19350</v>
       </c>
       <c r="S11" s="11">
         <f t="shared" si="18"/>
@@ -1672,15 +1672,15 @@
       </c>
       <c r="T11" s="11">
         <f t="shared" ca="1" si="18"/>
-        <v>0</v>
+        <v>3150</v>
       </c>
       <c r="U11" s="11">
         <f t="shared" ca="1" si="12"/>
-        <v>0</v>
+        <v>5175</v>
       </c>
       <c r="V11" s="11">
         <f t="shared" ca="1" si="12"/>
-        <v>4725</v>
+        <v>0</v>
       </c>
       <c r="W11" s="15">
         <f t="shared" ca="1" si="12"/>
@@ -1692,24 +1692,24 @@
       </c>
       <c r="Y11" s="18">
         <f t="shared" ca="1" si="14"/>
+        <v>31950</v>
+      </c>
+      <c r="Z11" s="18">
+        <f t="shared" ca="1" si="14"/>
+        <v>38025</v>
+      </c>
+      <c r="AA11" s="18">
+        <f t="shared" ca="1" si="14"/>
         <v>4950</v>
       </c>
-      <c r="Z11" s="18">
-        <f t="shared" ca="1" si="14"/>
-        <v>15750</v>
-      </c>
-      <c r="AA11" s="18">
-        <f t="shared" ca="1" si="14"/>
-        <v>36675</v>
-      </c>
       <c r="AB11" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>18900</v>
+        <v>19350</v>
       </c>
       <c r="AC11" s="16"/>
       <c r="AD11" s="2">
         <f t="shared" ca="1" si="19"/>
-        <v>102487.5</v>
+        <v>120487.5</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.3">
@@ -1727,19 +1727,19 @@
       </c>
       <c r="E12" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F12" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="H12" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="I12" s="7">
         <f t="shared" si="6"/>
@@ -1747,19 +1747,19 @@
       </c>
       <c r="J12" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="K12" s="7">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L12" s="7">
         <f t="shared" ca="1" si="9"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M12" s="7">
         <f t="shared" ca="1" si="10"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N12" s="9">
         <f t="shared" si="16"/>
@@ -1767,19 +1767,19 @@
       </c>
       <c r="O12" s="9">
         <f t="shared" ca="1" si="17"/>
-        <v>27000</v>
+        <v>34500</v>
       </c>
       <c r="P12" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>34000</v>
+        <v>32000</v>
       </c>
       <c r="Q12" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>24500</v>
+        <v>45000</v>
       </c>
       <c r="R12" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>28000</v>
+        <v>14500</v>
       </c>
       <c r="S12" s="11">
         <f t="shared" si="18"/>
@@ -1787,19 +1787,19 @@
       </c>
       <c r="T12" s="11">
         <f t="shared" ca="1" si="18"/>
-        <v>1000</v>
+        <v>4750</v>
       </c>
       <c r="U12" s="11">
         <f t="shared" ca="1" si="12"/>
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="V12" s="11">
         <f t="shared" ca="1" si="12"/>
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="W12" s="15">
         <f t="shared" ca="1" si="12"/>
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="X12" s="18">
         <f t="shared" si="13"/>
@@ -1807,24 +1807,24 @@
       </c>
       <c r="Y12" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>28000</v>
+        <v>39250</v>
       </c>
       <c r="Z12" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>38500</v>
+        <v>35500</v>
       </c>
       <c r="AA12" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>24500</v>
+        <v>55000</v>
       </c>
       <c r="AB12" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>29500</v>
+        <v>14500</v>
       </c>
       <c r="AC12" s="16"/>
       <c r="AD12" s="2">
         <f t="shared" ca="1" si="19"/>
-        <v>153000</v>
+        <v>176750</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.3">
@@ -1842,19 +1842,19 @@
       </c>
       <c r="E13" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F13" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="H13" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="I13" s="7">
         <f t="shared" si="6"/>
@@ -1866,11 +1866,11 @@
       </c>
       <c r="K13" s="7">
         <f t="shared" ca="1" si="8"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L13" s="7">
         <f t="shared" ca="1" si="9"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M13" s="7">
         <f t="shared" ca="1" si="10"/>
@@ -1882,19 +1882,19 @@
       </c>
       <c r="O13" s="9">
         <f t="shared" ca="1" si="17"/>
-        <v>8800</v>
+        <v>15400</v>
       </c>
       <c r="P13" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>34100</v>
+        <v>24200</v>
       </c>
       <c r="Q13" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>30250</v>
+        <v>8250</v>
       </c>
       <c r="R13" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>24200</v>
+        <v>18700</v>
       </c>
       <c r="S13" s="11">
         <f t="shared" si="18"/>
@@ -1906,11 +1906,11 @@
       </c>
       <c r="U13" s="11">
         <f t="shared" ca="1" si="12"/>
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="V13" s="11">
         <f t="shared" ca="1" si="12"/>
-        <v>1375</v>
+        <v>0</v>
       </c>
       <c r="W13" s="15">
         <f t="shared" ca="1" si="12"/>
@@ -1922,24 +1922,24 @@
       </c>
       <c r="Y13" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>8800</v>
+        <v>15400</v>
       </c>
       <c r="Z13" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>37400</v>
+        <v>24200</v>
       </c>
       <c r="AA13" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>31625</v>
+        <v>8250</v>
       </c>
       <c r="AB13" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>24200</v>
+        <v>18700</v>
       </c>
       <c r="AC13" s="16"/>
       <c r="AD13" s="2">
         <f t="shared" ca="1" si="19"/>
-        <v>138187.5</v>
+        <v>102712.5</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.3">
@@ -1957,19 +1957,19 @@
       </c>
       <c r="E14" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="F14" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H14" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="I14" s="7">
         <f t="shared" si="6"/>
@@ -1977,11 +1977,11 @@
       </c>
       <c r="J14" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K14" s="7">
         <f t="shared" ca="1" si="8"/>
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="L14" s="7">
         <f t="shared" ca="1" si="9"/>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="M14" s="7">
         <f t="shared" ca="1" si="10"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N14" s="9">
         <f t="shared" si="16"/>
@@ -1997,19 +1997,19 @@
       </c>
       <c r="O14" s="9">
         <f t="shared" ca="1" si="17"/>
-        <v>46800</v>
+        <v>11400</v>
       </c>
       <c r="P14" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>46200</v>
+        <v>25800</v>
       </c>
       <c r="Q14" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>26400</v>
+        <v>17400</v>
       </c>
       <c r="R14" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>21600</v>
+        <v>34800</v>
       </c>
       <c r="S14" s="11">
         <f t="shared" si="18"/>
@@ -2017,11 +2017,11 @@
       </c>
       <c r="T14" s="11">
         <f t="shared" ca="1" si="18"/>
-        <v>8400</v>
+        <v>0</v>
       </c>
       <c r="U14" s="11">
         <f t="shared" ca="1" si="12"/>
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="V14" s="11">
         <f t="shared" ca="1" si="12"/>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="W14" s="15">
         <f t="shared" ca="1" si="12"/>
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="X14" s="18">
         <f t="shared" si="13"/>
@@ -2037,24 +2037,24 @@
       </c>
       <c r="Y14" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>55200</v>
+        <v>11400</v>
       </c>
       <c r="Z14" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>54300</v>
+        <v>25800</v>
       </c>
       <c r="AA14" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>26400</v>
+        <v>17400</v>
       </c>
       <c r="AB14" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>21600</v>
+        <v>37200</v>
       </c>
       <c r="AC14" s="16"/>
       <c r="AD14" s="2">
         <f t="shared" ca="1" si="19"/>
-        <v>205500</v>
+        <v>139800</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.3">
@@ -2072,19 +2072,19 @@
       </c>
       <c r="E15" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="F15" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H15" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="I15" s="7">
         <f t="shared" si="6"/>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="J15" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K15" s="7">
         <f t="shared" ca="1" si="8"/>
@@ -2100,11 +2100,11 @@
       </c>
       <c r="L15" s="7">
         <f t="shared" ca="1" si="9"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M15" s="7">
         <f t="shared" ca="1" si="10"/>
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="N15" s="9">
         <f t="shared" si="16"/>
@@ -2112,19 +2112,19 @@
       </c>
       <c r="O15" s="9">
         <f t="shared" ca="1" si="17"/>
-        <v>21450</v>
+        <v>55900</v>
       </c>
       <c r="P15" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>11700</v>
+        <v>7150</v>
       </c>
       <c r="Q15" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>39000</v>
+        <v>31850</v>
       </c>
       <c r="R15" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>50700</v>
+        <v>9750</v>
       </c>
       <c r="S15" s="11">
         <f t="shared" si="18"/>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="T15" s="11">
         <f t="shared" ca="1" si="18"/>
-        <v>0</v>
+        <v>11700</v>
       </c>
       <c r="U15" s="11">
         <f t="shared" ca="1" si="12"/>
@@ -2140,11 +2140,11 @@
       </c>
       <c r="V15" s="11">
         <f t="shared" ca="1" si="12"/>
-        <v>3250</v>
+        <v>0</v>
       </c>
       <c r="W15" s="15">
         <f t="shared" ca="1" si="12"/>
-        <v>9100</v>
+        <v>0</v>
       </c>
       <c r="X15" s="18">
         <f t="shared" si="13"/>
@@ -2152,24 +2152,24 @@
       </c>
       <c r="Y15" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>21450</v>
+        <v>67600</v>
       </c>
       <c r="Z15" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>11700</v>
+        <v>7150</v>
       </c>
       <c r="AA15" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>42250</v>
+        <v>31850</v>
       </c>
       <c r="AB15" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>59800</v>
+        <v>9750</v>
       </c>
       <c r="AC15" s="16"/>
       <c r="AD15" s="2">
         <f t="shared" ca="1" si="19"/>
-        <v>187687.5</v>
+        <v>168837.5</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.3">
@@ -2187,19 +2187,19 @@
       </c>
       <c r="E16" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="F16" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="G16" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="H16" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="I16" s="7">
         <f t="shared" si="6"/>
@@ -2207,19 +2207,19 @@
       </c>
       <c r="J16" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K16" s="7">
         <f t="shared" ca="1" si="8"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L16" s="7">
         <f t="shared" ca="1" si="9"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M16" s="7">
         <f t="shared" ca="1" si="10"/>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="N16" s="9">
         <f t="shared" si="16"/>
@@ -2227,19 +2227,19 @@
       </c>
       <c r="O16" s="9">
         <f t="shared" ca="1" si="17"/>
-        <v>23100</v>
+        <v>41300</v>
       </c>
       <c r="P16" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>15400</v>
+        <v>49000</v>
       </c>
       <c r="Q16" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>8400</v>
+        <v>38500</v>
       </c>
       <c r="R16" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>11200</v>
+        <v>61600</v>
       </c>
       <c r="S16" s="11">
         <f t="shared" si="18"/>
@@ -2247,19 +2247,19 @@
       </c>
       <c r="T16" s="11">
         <f t="shared" ca="1" si="18"/>
-        <v>0</v>
+        <v>3150</v>
       </c>
       <c r="U16" s="11">
         <f t="shared" ca="1" si="12"/>
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="V16" s="11">
         <f t="shared" ca="1" si="12"/>
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="W16" s="15">
         <f t="shared" ca="1" si="12"/>
-        <v>0</v>
+        <v>13300</v>
       </c>
       <c r="X16" s="18">
         <f t="shared" si="13"/>
@@ -2267,24 +2267,24 @@
       </c>
       <c r="Y16" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>23100</v>
+        <v>44450</v>
       </c>
       <c r="Z16" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>15400</v>
+        <v>56000</v>
       </c>
       <c r="AA16" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>8400</v>
+        <v>40250</v>
       </c>
       <c r="AB16" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>11200</v>
+        <v>74900</v>
       </c>
       <c r="AC16" s="16"/>
       <c r="AD16" s="2">
         <f t="shared" ca="1" si="19"/>
-        <v>124600</v>
+        <v>282100</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.3">
@@ -2302,19 +2302,19 @@
       </c>
       <c r="E17" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="F17" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="G17" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="H17" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="I17" s="7">
         <f t="shared" si="6"/>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="J17" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K17" s="7">
         <f t="shared" ca="1" si="8"/>
@@ -2330,11 +2330,11 @@
       </c>
       <c r="L17" s="7">
         <f t="shared" ca="1" si="9"/>
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="M17" s="7">
         <f t="shared" ca="1" si="10"/>
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="N17" s="9">
         <f t="shared" si="16"/>
@@ -2342,19 +2342,19 @@
       </c>
       <c r="O17" s="9">
         <f t="shared" ca="1" si="17"/>
-        <v>51750</v>
+        <v>16500</v>
       </c>
       <c r="P17" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>25500</v>
+        <v>8250</v>
       </c>
       <c r="Q17" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>54750</v>
+        <v>31500</v>
       </c>
       <c r="R17" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>67500</v>
+        <v>53250</v>
       </c>
       <c r="S17" s="11">
         <f t="shared" si="18"/>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="T17" s="11">
         <f t="shared" ca="1" si="18"/>
-        <v>7125</v>
+        <v>0</v>
       </c>
       <c r="U17" s="11">
         <f t="shared" ca="1" si="12"/>
@@ -2370,11 +2370,11 @@
       </c>
       <c r="V17" s="11">
         <f t="shared" ca="1" si="12"/>
-        <v>8625</v>
+        <v>0</v>
       </c>
       <c r="W17" s="15">
         <f t="shared" ca="1" si="12"/>
-        <v>15000</v>
+        <v>7875</v>
       </c>
       <c r="X17" s="18">
         <f t="shared" si="13"/>
@@ -2382,24 +2382,24 @@
       </c>
       <c r="Y17" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>58875</v>
+        <v>16500</v>
       </c>
       <c r="Z17" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>25500</v>
+        <v>8250</v>
       </c>
       <c r="AA17" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>63375</v>
+        <v>31500</v>
       </c>
       <c r="AB17" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>82500</v>
+        <v>61125</v>
       </c>
       <c r="AC17" s="16"/>
       <c r="AD17" s="2">
         <f t="shared" ca="1" si="19"/>
-        <v>302062.5</v>
+        <v>189187.5</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.3">
@@ -2417,19 +2417,19 @@
       </c>
       <c r="E18" s="5">
         <f t="shared" ca="1" si="15"/>
+        <v>66</v>
+      </c>
+      <c r="F18" s="5">
+        <f t="shared" ca="1" si="15"/>
+        <v>16</v>
+      </c>
+      <c r="G18" s="5">
+        <f t="shared" ca="1" si="15"/>
+        <v>13</v>
+      </c>
+      <c r="H18" s="5">
+        <f t="shared" ca="1" si="15"/>
         <v>81</v>
-      </c>
-      <c r="F18" s="5">
-        <f t="shared" ca="1" si="15"/>
-        <v>33</v>
-      </c>
-      <c r="G18" s="5">
-        <f t="shared" ca="1" si="15"/>
-        <v>65</v>
-      </c>
-      <c r="H18" s="5">
-        <f t="shared" ca="1" si="15"/>
-        <v>51</v>
       </c>
       <c r="I18" s="7">
         <f t="shared" si="6"/>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="J18" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="K18" s="7">
         <f t="shared" ca="1" si="8"/>
@@ -2445,11 +2445,11 @@
       </c>
       <c r="L18" s="7">
         <f t="shared" ca="1" si="9"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M18" s="7">
         <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="N18" s="9">
         <f t="shared" si="16"/>
@@ -2457,19 +2457,19 @@
       </c>
       <c r="O18" s="9">
         <f t="shared" ca="1" si="17"/>
+        <v>56100</v>
+      </c>
+      <c r="P18" s="9">
+        <f t="shared" ca="1" si="11"/>
+        <v>13600</v>
+      </c>
+      <c r="Q18" s="9">
+        <f t="shared" ca="1" si="11"/>
+        <v>11050</v>
+      </c>
+      <c r="R18" s="9">
+        <f t="shared" ca="1" si="11"/>
         <v>68850</v>
-      </c>
-      <c r="P18" s="9">
-        <f t="shared" ca="1" si="11"/>
-        <v>28050</v>
-      </c>
-      <c r="Q18" s="9">
-        <f t="shared" ca="1" si="11"/>
-        <v>55250</v>
-      </c>
-      <c r="R18" s="9">
-        <f t="shared" ca="1" si="11"/>
-        <v>43350</v>
       </c>
       <c r="S18" s="11">
         <f t="shared" si="18"/>
@@ -2477,19 +2477,19 @@
       </c>
       <c r="T18" s="11">
         <f t="shared" ca="1" si="18"/>
+        <v>6800</v>
+      </c>
+      <c r="U18" s="11">
+        <f t="shared" ca="1" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="11">
+        <f t="shared" ca="1" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="15">
+        <f t="shared" ca="1" si="12"/>
         <v>13175</v>
-      </c>
-      <c r="U18" s="11">
-        <f t="shared" ca="1" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="V18" s="11">
-        <f t="shared" ca="1" si="12"/>
-        <v>6375</v>
-      </c>
-      <c r="W18" s="15">
-        <f t="shared" ca="1" si="12"/>
-        <v>425</v>
       </c>
       <c r="X18" s="18">
         <f t="shared" si="13"/>
@@ -2497,24 +2497,24 @@
       </c>
       <c r="Y18" s="18">
         <f t="shared" ca="1" si="14"/>
+        <v>62900</v>
+      </c>
+      <c r="Z18" s="18">
+        <f t="shared" ca="1" si="14"/>
+        <v>13600</v>
+      </c>
+      <c r="AA18" s="18">
+        <f t="shared" ca="1" si="14"/>
+        <v>11050</v>
+      </c>
+      <c r="AB18" s="18">
+        <f t="shared" ca="1" si="14"/>
         <v>82025</v>
-      </c>
-      <c r="Z18" s="18">
-        <f t="shared" ca="1" si="14"/>
-        <v>28050</v>
-      </c>
-      <c r="AA18" s="18">
-        <f t="shared" ca="1" si="14"/>
-        <v>61625</v>
-      </c>
-      <c r="AB18" s="18">
-        <f t="shared" ca="1" si="14"/>
-        <v>43775</v>
       </c>
       <c r="AC18" s="16"/>
       <c r="AD18" s="2">
         <f t="shared" ca="1" si="19"/>
-        <v>302600</v>
+        <v>256700</v>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.3">
@@ -2532,19 +2532,19 @@
       </c>
       <c r="E19" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F19" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="H19" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I19" s="7">
         <f t="shared" si="6"/>
@@ -2552,19 +2552,19 @@
       </c>
       <c r="J19" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K19" s="7">
         <f t="shared" ca="1" si="8"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L19" s="7">
         <f t="shared" ca="1" si="9"/>
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="M19" s="7">
         <f t="shared" ca="1" si="10"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N19" s="9">
         <f t="shared" si="16"/>
@@ -2572,19 +2572,19 @@
       </c>
       <c r="O19" s="9">
         <f t="shared" ca="1" si="17"/>
-        <v>44100</v>
+        <v>48600</v>
       </c>
       <c r="P19" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>29700</v>
+        <v>67500</v>
       </c>
       <c r="Q19" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>69300</v>
+        <v>15300</v>
       </c>
       <c r="R19" s="9">
         <f t="shared" ca="1" si="11"/>
-        <v>46800</v>
+        <v>49500</v>
       </c>
       <c r="S19" s="11">
         <f t="shared" si="18"/>
@@ -2592,19 +2592,19 @@
       </c>
       <c r="T19" s="11">
         <f t="shared" ca="1" si="18"/>
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="U19" s="11">
         <f t="shared" ca="1" si="12"/>
-        <v>0</v>
+        <v>11250</v>
       </c>
       <c r="V19" s="11">
         <f t="shared" ca="1" si="12"/>
-        <v>12150</v>
+        <v>0</v>
       </c>
       <c r="W19" s="15">
         <f t="shared" ca="1" si="12"/>
-        <v>900</v>
+        <v>2250</v>
       </c>
       <c r="X19" s="18">
         <f t="shared" si="13"/>
@@ -2612,24 +2612,24 @@
       </c>
       <c r="Y19" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>44100</v>
+        <v>50400</v>
       </c>
       <c r="Z19" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>29700</v>
+        <v>78750</v>
       </c>
       <c r="AA19" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>81450</v>
+        <v>15300</v>
       </c>
       <c r="AB19" s="18">
         <f t="shared" ca="1" si="14"/>
-        <v>47700</v>
+        <v>51750</v>
       </c>
       <c r="AC19" s="16"/>
       <c r="AD19" s="2">
         <f t="shared" ca="1" si="19"/>
-        <v>295875</v>
+        <v>289125</v>
       </c>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.3">
@@ -2647,19 +2647,19 @@
       </c>
       <c r="E20" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F20" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="H20" s="5">
         <f t="shared" ca="1" si="15"/>
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="I20" s="7">
         <f t="shared" si="6"/>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="J20" s="7">
         <f t="shared" ca="1" si="7"/>
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="K20" s="7">
         <f t="shared" ca="1" si="8"/>
@@ -2675,11 +2675,11 @@
       </c>
       <c r="L20" s="7">
         <f t="shared" ca="1" si="9"/>
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="M20" s="7">
         <f t="shared" ca="1" si="10"/>
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="N20" s="9">
         <f t="shared" si="16"/>
@@ -2687,19 +2687,19 @@
       </c>
       <c r="O20" s="9">
         <f t="shared" ca="1" si="17"/>
-        <v>71000</v>
+        <v>85000</v>
       </c>
       <c r="P20" s="9">
         <f t="shared" ref="P20" ca="1" si="20">$C20*F20</f>
-        <v>40000</v>
+        <v>30000</v>
       </c>
       <c r="Q20" s="9">
         <f t="shared" ref="Q20" ca="1" si="21">$C20*G20</f>
-        <v>79000</v>
+        <v>62000</v>
       </c>
       <c r="R20" s="9">
         <f t="shared" ref="R20" ca="1" si="22">$C20*H20</f>
-        <v>77000</v>
+        <v>23000</v>
       </c>
       <c r="S20" s="11">
         <f t="shared" si="18"/>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="T20" s="11">
         <f t="shared" ca="1" si="18"/>
-        <v>10500</v>
+        <v>17500</v>
       </c>
       <c r="U20" s="11">
         <f t="shared" ref="U20" ca="1" si="23">0.5*$C20*K20</f>
@@ -2715,11 +2715,11 @@
       </c>
       <c r="V20" s="11">
         <f t="shared" ref="V20" ca="1" si="24">0.5*$C20*L20</f>
-        <v>14500</v>
+        <v>6000</v>
       </c>
       <c r="W20" s="15">
         <f t="shared" ref="W20" ca="1" si="25">0.5*$C20*M20</f>
-        <v>13500</v>
+        <v>0</v>
       </c>
       <c r="X20" s="18">
         <f t="shared" si="13"/>
@@ -2727,24 +2727,24 @@
       </c>
       <c r="Y20" s="18">
         <f t="shared" ref="Y20:AB20" ca="1" si="26">O20+T20</f>
-        <v>81500</v>
+        <v>102500</v>
       </c>
       <c r="Z20" s="18">
         <f t="shared" ca="1" si="26"/>
-        <v>40000</v>
+        <v>30000</v>
       </c>
       <c r="AA20" s="18">
         <f t="shared" ca="1" si="26"/>
-        <v>93500</v>
+        <v>68000</v>
       </c>
       <c r="AB20" s="18">
         <f t="shared" ca="1" si="26"/>
-        <v>90500</v>
+        <v>23000</v>
       </c>
       <c r="AC20" s="16"/>
       <c r="AD20" s="2">
         <f t="shared" ca="1" si="19"/>
-        <v>415500</v>
+        <v>333500</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.3">
@@ -2759,41 +2759,41 @@
         <f>MAX(D4:D20)</f>
         <v>90</v>
       </c>
-      <c r="E22" s="20">
+      <c r="E22" s="19">
         <f t="shared" ref="E22:AB22" ca="1" si="27">MAX(E4:E20)</f>
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F22" s="3">
         <f t="shared" ca="1" si="27"/>
-        <v>82</v>
-      </c>
-      <c r="G22" s="21">
+        <v>90</v>
+      </c>
+      <c r="G22" s="20">
         <f t="shared" ca="1" si="27"/>
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H22" s="3">
         <f t="shared" ca="1" si="27"/>
-        <v>90</v>
-      </c>
-      <c r="I22" s="21">
+        <v>88</v>
+      </c>
+      <c r="I22" s="20">
         <f t="shared" si="27"/>
         <v>40</v>
       </c>
       <c r="J22" s="3">
         <f t="shared" ca="1" si="27"/>
-        <v>34</v>
-      </c>
-      <c r="K22" s="21">
+        <v>36</v>
+      </c>
+      <c r="K22" s="20">
         <f t="shared" ca="1" si="27"/>
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L22" s="3">
         <f t="shared" ca="1" si="27"/>
-        <v>31</v>
-      </c>
-      <c r="M22" s="21">
+        <v>40</v>
+      </c>
+      <c r="M22" s="20">
         <f t="shared" ca="1" si="27"/>
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="N22" s="1">
         <f t="shared" si="27"/>
@@ -2801,19 +2801,19 @@
       </c>
       <c r="O22" s="2">
         <f t="shared" ca="1" si="27"/>
-        <v>71000</v>
+        <v>85000</v>
       </c>
       <c r="P22" s="3">
         <f t="shared" ca="1" si="27"/>
-        <v>46200</v>
+        <v>67500</v>
       </c>
       <c r="Q22" s="2">
         <f t="shared" ca="1" si="27"/>
-        <v>79000</v>
+        <v>62000</v>
       </c>
       <c r="R22" s="3">
         <f t="shared" ca="1" si="27"/>
-        <v>77000</v>
+        <v>68850</v>
       </c>
       <c r="S22" s="2">
         <f t="shared" si="27"/>
@@ -2821,19 +2821,19 @@
       </c>
       <c r="T22" s="3">
         <f t="shared" ca="1" si="27"/>
-        <v>13175</v>
+        <v>17500</v>
       </c>
       <c r="U22" s="2">
         <f t="shared" ca="1" si="27"/>
-        <v>8100</v>
+        <v>11250</v>
       </c>
       <c r="V22" s="1">
         <f t="shared" ca="1" si="27"/>
-        <v>14500</v>
+        <v>10000</v>
       </c>
       <c r="W22" s="2">
         <f t="shared" ca="1" si="27"/>
-        <v>15000</v>
+        <v>13300</v>
       </c>
       <c r="X22" s="3">
         <f t="shared" si="27"/>
@@ -2841,24 +2841,24 @@
       </c>
       <c r="Y22" s="2">
         <f t="shared" ca="1" si="27"/>
-        <v>82025</v>
+        <v>102500</v>
       </c>
       <c r="Z22" s="1">
         <f t="shared" ca="1" si="27"/>
-        <v>54300</v>
+        <v>78750</v>
       </c>
       <c r="AA22" s="2">
         <f t="shared" ca="1" si="27"/>
-        <v>93500</v>
+        <v>68000</v>
       </c>
       <c r="AB22" s="1">
         <f t="shared" ca="1" si="27"/>
-        <v>90500</v>
+        <v>82025</v>
       </c>
       <c r="AC22" s="1"/>
       <c r="AD22" s="1">
         <f t="shared" ref="AD22" ca="1" si="28">MAX(AD4:AD20)</f>
-        <v>415500</v>
+        <v>333500</v>
       </c>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.3">
@@ -2873,23 +2873,23 @@
         <f>MIN(D4:D20)</f>
         <v>40</v>
       </c>
-      <c r="E23" s="20">
+      <c r="E23" s="19">
         <f t="shared" ref="E23:AB23" ca="1" si="29">MIN(E4:E20)</f>
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F23" s="3">
         <f t="shared" ca="1" si="29"/>
-        <v>18</v>
-      </c>
-      <c r="G23" s="21">
+        <v>11</v>
+      </c>
+      <c r="G23" s="20">
         <f t="shared" ca="1" si="29"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H23" s="3">
         <f t="shared" ca="1" si="29"/>
-        <v>16</v>
-      </c>
-      <c r="I23" s="21">
+        <v>13</v>
+      </c>
+      <c r="I23" s="20">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
@@ -2897,7 +2897,7 @@
         <f t="shared" ca="1" si="29"/>
         <v>0</v>
       </c>
-      <c r="K23" s="21">
+      <c r="K23" s="20">
         <f t="shared" ca="1" si="29"/>
         <v>0</v>
       </c>
@@ -2905,7 +2905,7 @@
         <f t="shared" ca="1" si="29"/>
         <v>0</v>
       </c>
-      <c r="M23" s="21">
+      <c r="M23" s="20">
         <f t="shared" ca="1" si="29"/>
         <v>0</v>
       </c>
@@ -2915,19 +2915,19 @@
       </c>
       <c r="O23" s="2">
         <f t="shared" ca="1" si="29"/>
-        <v>4950</v>
+        <v>4700</v>
       </c>
       <c r="P23" s="3">
         <f t="shared" ca="1" si="29"/>
-        <v>4000</v>
+        <v>3600</v>
       </c>
       <c r="Q23" s="2">
         <f t="shared" ca="1" si="29"/>
-        <v>3100</v>
+        <v>4950</v>
       </c>
       <c r="R23" s="3">
         <f t="shared" ca="1" si="29"/>
-        <v>1600</v>
+        <v>2600</v>
       </c>
       <c r="S23" s="2">
         <f t="shared" si="29"/>
@@ -2955,24 +2955,24 @@
       </c>
       <c r="Y23" s="2">
         <f t="shared" ca="1" si="29"/>
-        <v>4950</v>
+        <v>4700</v>
       </c>
       <c r="Z23" s="1">
         <f t="shared" ca="1" si="29"/>
-        <v>4000</v>
+        <v>3600</v>
       </c>
       <c r="AA23" s="2">
         <f t="shared" ca="1" si="29"/>
-        <v>3100</v>
+        <v>4950</v>
       </c>
       <c r="AB23" s="1">
         <f t="shared" ca="1" si="29"/>
-        <v>1600</v>
+        <v>2600</v>
       </c>
       <c r="AC23" s="1"/>
       <c r="AD23" s="1">
         <f t="shared" ref="AD23" ca="1" si="30">MIN(AD4:AD20)</f>
-        <v>19200</v>
+        <v>26900</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.3">
@@ -2987,41 +2987,41 @@
         <f>AVERAGE(D4:D20)</f>
         <v>62.588235294117645</v>
       </c>
-      <c r="E24" s="20">
+      <c r="E24" s="19">
         <f t="shared" ref="E24:AB24" ca="1" si="31">AVERAGE(E4:E20)</f>
-        <v>55.941176470588232</v>
+        <v>51.529411764705884</v>
       </c>
       <c r="F24" s="3">
         <f t="shared" ca="1" si="31"/>
-        <v>47.823529411764703</v>
-      </c>
-      <c r="G24" s="21">
+        <v>46.294117647058826</v>
+      </c>
+      <c r="G24" s="20">
         <f t="shared" ca="1" si="31"/>
-        <v>55.705882352941174</v>
+        <v>49.705882352941174</v>
       </c>
       <c r="H24" s="3">
         <f t="shared" ca="1" si="31"/>
-        <v>49</v>
-      </c>
-      <c r="I24" s="21">
+        <v>52.529411764705884</v>
+      </c>
+      <c r="I24" s="20">
         <f t="shared" si="31"/>
         <v>14.294117647058824</v>
       </c>
       <c r="J24" s="3">
         <f t="shared" ca="1" si="31"/>
-        <v>12.764705882352942</v>
-      </c>
-      <c r="K24" s="21">
+        <v>9.8235294117647065</v>
+      </c>
+      <c r="K24" s="20">
         <f t="shared" ca="1" si="31"/>
         <v>8.5882352941176467</v>
       </c>
       <c r="L24" s="3">
         <f t="shared" ca="1" si="31"/>
-        <v>11.647058823529411</v>
-      </c>
-      <c r="M24" s="21">
+        <v>11.058823529411764</v>
+      </c>
+      <c r="M24" s="20">
         <f t="shared" ca="1" si="31"/>
-        <v>8.6470588235294112</v>
+        <v>11.705882352941176</v>
       </c>
       <c r="N24" s="1">
         <f t="shared" si="31"/>
@@ -3029,19 +3029,19 @@
       </c>
       <c r="O24" s="2">
         <f t="shared" ca="1" si="31"/>
-        <v>28135.294117647059</v>
+        <v>27485.294117647059</v>
       </c>
       <c r="P24" s="3">
         <f t="shared" ca="1" si="31"/>
-        <v>21923.529411764706</v>
+        <v>21861.764705882353</v>
       </c>
       <c r="Q24" s="2">
         <f t="shared" ca="1" si="31"/>
-        <v>30191.176470588234</v>
+        <v>22055.882352941175</v>
       </c>
       <c r="R24" s="3">
         <f t="shared" ca="1" si="31"/>
-        <v>27100</v>
+        <v>27141.176470588234</v>
       </c>
       <c r="S24" s="2">
         <f t="shared" si="31"/>
@@ -3049,19 +3049,19 @@
       </c>
       <c r="T24" s="3">
         <f t="shared" ca="1" si="31"/>
-        <v>3135.294117647059</v>
+        <v>3023.5294117647059</v>
       </c>
       <c r="U24" s="2">
         <f t="shared" ca="1" si="31"/>
-        <v>1513.2352941176471</v>
+        <v>2029.4117647058824</v>
       </c>
       <c r="V24" s="1">
         <f t="shared" ca="1" si="31"/>
-        <v>3573.5294117647059</v>
+        <v>1873.5294117647059</v>
       </c>
       <c r="W24" s="2">
         <f t="shared" ca="1" si="31"/>
-        <v>2666.1764705882351</v>
+        <v>3155.8823529411766</v>
       </c>
       <c r="X24" s="3">
         <f t="shared" si="31"/>
@@ -3069,24 +3069,24 @@
       </c>
       <c r="Y24" s="2">
         <f t="shared" ca="1" si="31"/>
-        <v>31270.588235294119</v>
+        <v>30508.823529411766</v>
       </c>
       <c r="Z24" s="1">
         <f t="shared" ca="1" si="31"/>
-        <v>23436.764705882353</v>
+        <v>23891.176470588234</v>
       </c>
       <c r="AA24" s="2">
         <f t="shared" ca="1" si="31"/>
-        <v>33764.705882352944</v>
+        <v>23929.411764705881</v>
       </c>
       <c r="AB24" s="1">
         <f t="shared" ca="1" si="31"/>
-        <v>29766.176470588234</v>
+        <v>30297.058823529413</v>
       </c>
       <c r="AC24" s="1"/>
       <c r="AD24" s="1">
         <f t="shared" ref="AD24" ca="1" si="32">AVERAGE(AD4:AD20)</f>
-        <v>159999.26470588235</v>
+        <v>150387.5</v>
       </c>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.3">
@@ -3101,41 +3101,41 @@
         <f>SUM(D4:D20)</f>
         <v>1064</v>
       </c>
-      <c r="E25" s="20">
+      <c r="E25" s="19">
         <f t="shared" ref="E25:AB25" ca="1" si="33">SUM(E4:E20)</f>
-        <v>951</v>
+        <v>876</v>
       </c>
       <c r="F25" s="3">
         <f t="shared" ca="1" si="33"/>
-        <v>813</v>
-      </c>
-      <c r="G25" s="21">
+        <v>787</v>
+      </c>
+      <c r="G25" s="20">
         <f t="shared" ca="1" si="33"/>
-        <v>947</v>
+        <v>845</v>
       </c>
       <c r="H25" s="3">
         <f t="shared" ca="1" si="33"/>
-        <v>833</v>
-      </c>
-      <c r="I25" s="21">
+        <v>893</v>
+      </c>
+      <c r="I25" s="20">
         <f t="shared" si="33"/>
         <v>243</v>
       </c>
       <c r="J25" s="3">
         <f t="shared" ca="1" si="33"/>
-        <v>217</v>
-      </c>
-      <c r="K25" s="21">
+        <v>167</v>
+      </c>
+      <c r="K25" s="20">
         <f t="shared" ca="1" si="33"/>
         <v>146</v>
       </c>
       <c r="L25" s="3">
         <f t="shared" ca="1" si="33"/>
-        <v>198</v>
-      </c>
-      <c r="M25" s="21">
+        <v>188</v>
+      </c>
+      <c r="M25" s="20">
         <f t="shared" ca="1" si="33"/>
-        <v>147</v>
+        <v>199</v>
       </c>
       <c r="N25" s="1">
         <f t="shared" si="33"/>
@@ -3143,19 +3143,19 @@
       </c>
       <c r="O25" s="2">
         <f t="shared" ca="1" si="33"/>
-        <v>478300</v>
+        <v>467250</v>
       </c>
       <c r="P25" s="3">
         <f t="shared" ca="1" si="33"/>
-        <v>372700</v>
+        <v>371650</v>
       </c>
       <c r="Q25" s="2">
         <f t="shared" ca="1" si="33"/>
-        <v>513250</v>
+        <v>374950</v>
       </c>
       <c r="R25" s="3">
         <f t="shared" ca="1" si="33"/>
-        <v>460700</v>
+        <v>461400</v>
       </c>
       <c r="S25" s="2">
         <f t="shared" si="33"/>
@@ -3163,19 +3163,19 @@
       </c>
       <c r="T25" s="3">
         <f t="shared" ca="1" si="33"/>
-        <v>53300</v>
+        <v>51400</v>
       </c>
       <c r="U25" s="2">
         <f t="shared" ca="1" si="33"/>
-        <v>25725</v>
+        <v>34500</v>
       </c>
       <c r="V25" s="1">
         <f t="shared" ca="1" si="33"/>
-        <v>60750</v>
+        <v>31850</v>
       </c>
       <c r="W25" s="2">
         <f t="shared" ca="1" si="33"/>
-        <v>45325</v>
+        <v>53650</v>
       </c>
       <c r="X25" s="3">
         <f t="shared" si="33"/>
@@ -3183,24 +3183,24 @@
       </c>
       <c r="Y25" s="2">
         <f t="shared" ca="1" si="33"/>
-        <v>531600</v>
+        <v>518650</v>
       </c>
       <c r="Z25" s="1">
         <f t="shared" ca="1" si="33"/>
-        <v>398425</v>
+        <v>406150</v>
       </c>
       <c r="AA25" s="2">
         <f t="shared" ca="1" si="33"/>
-        <v>574000</v>
+        <v>406800</v>
       </c>
       <c r="AB25" s="1">
         <f t="shared" ca="1" si="33"/>
-        <v>506025</v>
+        <v>515050</v>
       </c>
       <c r="AC25" s="1"/>
       <c r="AD25" s="1">
         <f t="shared" ref="AD25" ca="1" si="34">SUM(AD4:AD20)</f>
-        <v>2719987.5</v>
+        <v>2556587.5</v>
       </c>
     </row>
   </sheetData>
@@ -3209,5 +3209,8 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="25" orientation="landscape" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="D22:D25" formulaRange="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>